--- a/Soal_Kuis.xlsx
+++ b/Soal_Kuis.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,32 +459,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Apa faktor utama yang memengaruhi besarnya energi kinetik pada suatu benda?</t>
+          <t>Apa arti pokok dari ajaran bahwa manusia diciptakan sebagai 'Citra Allah'?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Massa dan Posisi</t>
+          <t>Manusia memiliki wajah yang persis sama dengan Allah</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Kecepatan dan Ketinggian</t>
+          <t>Manusia adalah malaikat yang turun ke bumi</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Massa dan Kecepatan</t>
+          <t>Manusia dibekali akal budi, kehendak bebas, dan cinta kasih</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Waktu dan Jarak</t>
+          <t>Manusia tidak pernah bisa berbuat dosa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Massa dan Kecepatan</t>
+          <t>Manusia dibekali akal budi, kehendak bebas, dan cinta kasih</t>
         </is>
       </c>
     </row>
@@ -494,32 +494,662 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kelereng yang jatuh dari meja tinggi terasa lebih sakit. Hal ini berkaitan dengan perubahan energi...</t>
+          <t>Kisah penciptaan manusia sebagai Citra Allah (Imago Dei) dapat kita temukan di dalam Kitab Suci pada kitab...</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kinetik menjadi Potensial</t>
+          <t>Kejadian 1:26-27</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Potensial menjadi Kinetik</t>
+          <t>Keluaran 20:1-17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mekanik menjadi Panas</t>
+          <t>Matius 5:1-12</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gerak menjadi Bunyi</t>
+          <t>Mazmur 23:1-6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Potensial menjadi Kinetik</t>
+          <t>Kejadian 1:26-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Salah satu perbedaan utama yang mendasar antara manusia dengan ciptaan Allah lainnya adalah...</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Manusia memiliki insting untuk bertahan hidup</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Manusia membutuhkan makanan untuk hidup</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Manusia memiliki akal budi dan kehendak bebas</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Manusia bisa berkembang biak</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Manusia memiliki akal budi dan kehendak bebas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Karena setiap manusia adalah Citra Allah, maka sikap yang paling tepat terhadap teman yang berbeda suku atau kondisi fisiknya adalah...</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Menghindarinya agar tidak terjadi konflik</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Menghormati martabatnya sebagai sesama ciptaan</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Hanya berteman jika memiliki agama yang sama</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Merasa diri lebih baik dari mereka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Menghormati martabatnya sebagai sesama ciptaan</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Manusia diberi kuasa oleh Allah atas ciptaan lainnya (hewan, tumbuhan, alam). Kuasa ini harus dijalankan dengan sikap...</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Mengeksploitasi alam demi kekayaan</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Tanggung jawab dan cinta kasih sebagai pemelihara</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Mengabaikan alam karena akan hancur pada akhirnya</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Menggunakan sumber daya alam hanya untuk golongan tertentu</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tanggung jawab dan cinta kasih sebagai pemelihara</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kesederajatan antara laki-laki dan perempuan secara simbolis ditunjukkan dalam kisah penciptaan perempuan yang diambil dari...</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Tanah liat yang dibentuk</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Tulang rusuk laki-laki</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Pohon pengetahuan yang baik dan jahat</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Napas kehidupan langsung dari surga</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tulang rusuk laki-laki</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kemampuan istimewa manusia sebagai Citra Allah yang memungkinkannya membedakan perbuatan baik dan buruk disebut...</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Hati nurani</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Naluri</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Insting hewani</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Hukum alam</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hati nurani</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Siapakah sosok 'Citra Allah' yang paling sempurna, yang menjelma menjadi manusia untuk menjadi teladan hidup bagi umat Kristiani?</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Santo Petrus</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Bunda Maria</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Yesus Kristus</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nabi Musa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Yesus Kristus</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tindakan di bawah ini yang merupakan bentuk perusakan terhadap martabat manusia sebagai Citra Allah adalah...</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Membantu teman yang kesulitan belajar</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Melakukan perundungan (bullying) kepada teman</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Menjaga kebersihan lingkungan sekolah</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Menghormati orang tua dan guru</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Melakukan perundungan (bullying) kepada teman</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sikap bersyukur yang paling tepat atas anugerahkan tubuh dan talenta dari Allah adalah...</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Membiarkannya tanpa dikembangkan</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Merawat, menjaga kesehatan, dan melatih bakat</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Menyombongkannya kepada orang lain</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Merasa malu dengan kekurangan diri</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Merawat, menjaga kesehatan, dan melatih bakat</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Manusia sering disebut sebagai 'mahkota ciptaan' karena...</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Manusia memiliki mahkota di kepalanya</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Manusia menguasai teknologi tertinggi</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Diciptakan paling akhir dan serupa dengan Allah</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Manusia memiliki jumlah paling banyak di bumi</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Diciptakan paling akhir dan serupa dengan Allah</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Manusia tidak bisa hidup sendirian dan selalu membutuhkan orang lain. Hal ini menunjukkan bahwa manusia diciptakan sebagai makhluk...</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Individu</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Sosial</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Egois</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sosial</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ajaran Gereja Katolik sangat menjunjung tinggi kesucian hidup manusia. Oleh karena itu, kehidupan manusia harus dilindungi sejak dari...</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Masa remaja hingga dewasa</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Dalam kandungan ibu hingga kematian alami</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Saat mulai bersekolah hingga tua</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Saat manusia bisa berpikir sendiri</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dalam kandungan ibu hingga kematian alami</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Apa yang dimaksud dengan anugerah 'kehendak bebas' (free will) dari Allah kepada manusia?</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Kebebasan untuk melakukan dosa tanpa batas</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Kebebasan memilih yang baik sesuai kehendak Allah</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Hak untuk menentukan agama orang lain</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kewajiban untuk tunduk pada penguasa dunia</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Kebebasan memilih yang baik sesuai kehendak Allah</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Tubuh manusia dihormati dalam ajaran Katolik dan tidak boleh dirusak karena tubuh kita merupakan...</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Sumber segala dosa</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Bait Roh Kudus</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Hanya sementara dan tidak berguna</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Milik pribadi yang bebas diubah-ubah</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Bait Roh Kudus</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Perbedaan bakat, sifat, dan kemampuan antara satu individu dengan individu lainnya menunjukkan bahwa ciptaan Allah itu...</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Unik dan saling melengkapi</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Berbeda kasta dan kedudukan</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Tidak setara di mata Tuhan</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Satu-satunya yang tidak pernah berbuat dosa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Unik dan saling melengkapi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Salah satu bentuk pelanggaran berat terhadap hak asasi manusia yang sangat bertentangan dengan martabat Citra Allah adalah...</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Memberikan sedekah kepada pengemis</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Perdagangan manusia (human trafficking)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Mendirikan panti asuhan</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mengikuti kegiatan retret sekolah</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Perdagangan manusia (human trafficking)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ajaran Sosial Gereja sangat menekankan perlindungan terhadap martabat manusia, terutama kepada mereka yang...</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Kaya dan berkuasa</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Memiliki jabatan di pemerintahan</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Lemah, miskin, dan tersingkir (marginal)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Rajin pergi ke gereja setiap minggu</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lemah, miskin, dan tersingkir (marginal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tugas utama manusia sebagai Citra Allah di tengah dunia ini adalah...</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Menjadi penguasa mutlak atas bumi</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Mewujudkan cinta kasih Allah kepada sesama dan ciptaan</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Mencari ketenaran sebanyak-banyaknya</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Menikmati seluruh fasilitas yang ada di bumi</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Mewujudkan cinta kasih Allah kepada sesama dan ciptaan</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Tujuan akhir dari kehidupan manusia yang diciptakan sesuai dengan Citra Allah adalah...</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Menjadi kaya raya di dunia</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Bersatu dan memuliakan Allah Bapa di Surga</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mencapai kebahagiaan tanpa penderitaan</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Reinkarnasi menjadi manusia yang lebih baik</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Bersatu dan memuliakan Allah Bapa di Surga</t>
         </is>
       </c>
     </row>
